--- a/data/stx_xlsx/SFRG.ST.xlsx
+++ b/data/stx_xlsx/SFRG.ST.xlsx
@@ -7487,11 +7487,26 @@
       <c r="B48" s="15">
         <v>155.27</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
+      <c r="C48" s="16">
+        <f t="shared" ref="C48:G48" si="1">SUM(C51:C53)</f>
+        <v>116.18</v>
+      </c>
+      <c r="D48" s="16">
+        <f t="shared" si="1"/>
+        <v>91.62</v>
+      </c>
+      <c r="E48" s="16">
+        <f t="shared" si="1"/>
+        <v>101.66</v>
+      </c>
+      <c r="F48" s="16">
+        <f t="shared" si="1"/>
+        <v>123.73</v>
+      </c>
+      <c r="G48" s="16">
+        <f t="shared" si="1"/>
+        <v>117.99</v>
+      </c>
       <c r="H48" s="16">
         <v>70.32</v>
       </c>
